--- a/Excel Day 3.xlsx
+++ b/Excel Day 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\excel_task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E95B30D-72B8-48E7-A6C2-D6186168E8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D30F6B-7193-4D99-AB32-F8B9269F0BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{609FEBEB-89AE-4A96-B106-CF1FC4532DFB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{609FEBEB-89AE-4A96-B106-CF1FC4532DFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8136" uniqueCount="1898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8163" uniqueCount="1913">
   <si>
     <t>Emp Id</t>
   </si>
@@ -5734,13 +5756,61 @@
     <t>nested if</t>
   </si>
   <si>
-    <t>switch</t>
+    <t>&gt;=900</t>
+  </si>
+  <si>
+    <t>&lt;=800</t>
+  </si>
+  <si>
+    <t>&gt;800</t>
+  </si>
+  <si>
+    <t>ifs</t>
+  </si>
+  <si>
+    <t>sumif</t>
+  </si>
+  <si>
+    <t>average sal female</t>
+  </si>
+  <si>
+    <t>average  sal male</t>
+  </si>
+  <si>
+    <t>average salary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total male salary </t>
+  </si>
+  <si>
+    <t>Total female salary</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>female</t>
+  </si>
+  <si>
+    <t>male</t>
+  </si>
+  <si>
+    <t>china</t>
+  </si>
+  <si>
+    <t>Total Salary using  sumifs</t>
+  </si>
+  <si>
+    <t>Total employe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5758,7 +5828,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5789,8 +5859,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -5813,11 +5889,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5833,13 +5924,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6190,8 +6287,12 @@
     <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="16" thickBot="1" x14ac:dyDescent="0.4">
@@ -6269,14 +6370,14 @@
       <c r="L2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="O2" s="10" t="s">
         <v>1879</v>
       </c>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
     </row>
     <row r="3" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
@@ -6360,6 +6461,13 @@
         <f>SUM(sal)</f>
         <v>101965674</v>
       </c>
+      <c r="R4" s="6" t="s">
+        <v>1902</v>
+      </c>
+      <c r="S4" s="9">
+        <f>AVERAGEIF(F2:F901,"female",J2:J901)</f>
+        <v>112667.98047722342</v>
+      </c>
     </row>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
@@ -6398,6 +6506,9 @@
       <c r="L5" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="M5" t="s">
+        <v>1907</v>
+      </c>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
@@ -6436,6 +6547,9 @@
       <c r="L6" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="M6" t="s">
+        <v>1908</v>
+      </c>
       <c r="O6" s="6" t="s">
         <v>1876</v>
       </c>
@@ -6443,6 +6557,13 @@
         <f>AVERAGE(sal)</f>
         <v>113295.19333333333</v>
       </c>
+      <c r="R6" s="6" t="s">
+        <v>1903</v>
+      </c>
+      <c r="S6" s="9">
+        <f>AVERAGEIF(F2:F901,"male",J2:J901)</f>
+        <v>113953.83826879271</v>
+      </c>
     </row>
     <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
@@ -6526,6 +6647,13 @@
         <f>MIN(sal)</f>
         <v>40063</v>
       </c>
+      <c r="R8" s="6" t="s">
+        <v>1904</v>
+      </c>
+      <c r="S8">
+        <f>AVERAGE(J2:J901)</f>
+        <v>113295.19333333333</v>
+      </c>
     </row>
     <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
@@ -6768,6 +6896,13 @@
       <c r="L14" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="O14" s="6" t="s">
+        <v>1905</v>
+      </c>
+      <c r="P14">
+        <f>SUMIF(F2:F901,"male",J2:J901)</f>
+        <v>50025735</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
@@ -6844,8 +6979,15 @@
       <c r="L16" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="O16" s="6" t="s">
+        <v>1906</v>
+      </c>
+      <c r="P16">
+        <f>SUMIF(F2:F901,"female",J2:J901)</f>
+        <v>51939939</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
         <v>85</v>
       </c>
@@ -6883,7 +7025,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
         <v>88</v>
       </c>
@@ -6921,7 +7063,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>90</v>
       </c>
@@ -6959,7 +7101,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
         <v>93</v>
       </c>
@@ -6996,8 +7138,13 @@
       <c r="L20" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="11" t="s">
+        <v>1911</v>
+      </c>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
         <v>95</v>
       </c>
@@ -7034,8 +7181,11 @@
       <c r="L21" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P21" s="11"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
         <v>97</v>
       </c>
@@ -7072,8 +7222,18 @@
       <c r="L22" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P22" s="12" t="s">
+        <v>1909</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="R22" s="12">
+        <f>SUMIFS($J$2:$J$901,$F$2:$F$901,P22,$K$2:$K$901,Q22)</f>
+        <v>11696706</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
         <v>100</v>
       </c>
@@ -7110,8 +7270,18 @@
       <c r="L23" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P23" s="12" t="s">
+        <v>1908</v>
+      </c>
+      <c r="Q23" s="12" t="s">
+        <v>1910</v>
+      </c>
+      <c r="R23" s="12">
+        <f>SUMIFS($J$2:$J$901,$F$2:$F$901,P23,$K$2:$K$901,Q23)</f>
+        <v>11502870</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
         <v>103</v>
       </c>
@@ -7148,8 +7318,18 @@
       <c r="L24" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P24" s="12" t="s">
+        <v>1909</v>
+      </c>
+      <c r="Q24" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" s="12">
+        <f>SUMIFS($J$2:$J$901,$F$2:$F$901,P24,$K$2:$K$901,Q24)</f>
+        <v>31237217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2" t="s">
         <v>107</v>
       </c>
@@ -7186,8 +7366,18 @@
       <c r="L25" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P25" s="12" t="s">
+        <v>1908</v>
+      </c>
+      <c r="Q25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="R25" s="12">
+        <f>SUMIFS($J$2:$J$901,$F$2:$F$901,P25,$K$2:$K$901,Q25)</f>
+        <v>33013815</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
         <v>110</v>
       </c>
@@ -7224,8 +7414,18 @@
       <c r="L26" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P26" s="12" t="s">
+        <v>1909</v>
+      </c>
+      <c r="Q26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="R26" s="12">
+        <f t="shared" ref="R26:R27" si="0">SUMIFS($J$2:$J$901,$F$2:$F$901,P26,$K$2:$K$901,Q26)</f>
+        <v>7091812</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
         <v>112</v>
       </c>
@@ -7262,8 +7462,22 @@
       <c r="L27" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P27" s="12" t="s">
+        <v>1908</v>
+      </c>
+      <c r="Q27" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="R27" s="12">
+        <f t="shared" si="0"/>
+        <v>7423254</v>
+      </c>
+      <c r="S27">
+        <f>SUMIFS(J2:J901,F2:F901,P27,K2:K901,Q27)</f>
+        <v>7423254</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
         <v>114</v>
       </c>
@@ -7301,7 +7515,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
         <v>117</v>
       </c>
@@ -7339,7 +7553,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
         <v>119</v>
       </c>
@@ -7376,8 +7590,15 @@
       <c r="L30" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N30" s="12" t="s">
+        <v>1912</v>
+      </c>
+      <c r="O30" s="12">
+        <f>COUNT(H2:H901)</f>
+        <v>900</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2" t="s">
         <v>121</v>
       </c>
@@ -7414,8 +7635,15 @@
       <c r="L31" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N31" s="12" t="s">
+        <v>1909</v>
+      </c>
+      <c r="O31" s="12">
+        <f>COUNTIF(F2:F901,F881)</f>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>123</v>
       </c>
@@ -7451,6 +7679,13 @@
       </c>
       <c r="L32" s="3" t="s">
         <v>42</v>
+      </c>
+      <c r="N32" s="12" t="s">
+        <v>1908</v>
+      </c>
+      <c r="O32" s="12">
+        <f>COUNTIF(F2:F901,F882)</f>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -40476,8 +40711,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="O2:T2"/>
+    <mergeCell ref="P20:R21"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:L1">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
@@ -40496,7 +40732,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E56ACB3-91FF-4022-9E6B-3E4F08EC8D82}">
-  <dimension ref="C6:N12"/>
+  <dimension ref="C6:Q12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -40509,46 +40745,49 @@
     <col min="10" max="10" width="10.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C6" s="8" t="s">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C6" s="7" t="s">
         <v>1880</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>1881</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>1882</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>1883</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>1884</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>1885</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>1886</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>1887</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>1894</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="7" t="s">
         <v>1895</v>
       </c>
-      <c r="M6" s="8" t="s">
+      <c r="M6" s="7" t="s">
         <v>1896</v>
       </c>
-      <c r="N6" s="8" t="s">
-        <v>1897</v>
-      </c>
-    </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C7" s="9" t="s">
+      <c r="N6" s="7" t="s">
+        <v>1900</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C7" s="8" t="s">
         <v>1888</v>
       </c>
       <c r="D7">
@@ -40577,12 +40816,27 @@
         <v>979</v>
       </c>
       <c r="L7" t="str">
-        <f>IF(K7&gt;900,"high","low")</f>
+        <f>IF(K7&gt;=900,"High","Low")</f>
+        <v>High</v>
+      </c>
+      <c r="M7" t="str">
+        <f>IF(K7&gt;=900,"High",IF(K7&lt;=800,"Low","Mid"))</f>
+        <v>High</v>
+      </c>
+      <c r="N7" t="str" cm="1">
+        <f t="array" ref="N7">_xlfn.IFS(K7&gt;=900,"high",K7&lt;900,"low")</f>
         <v>high</v>
       </c>
-    </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C8" s="9" t="s">
+      <c r="O7">
+        <f>SUMIFS(I7:I12,K7:K12,"&gt;750",L7:L12,"High")</f>
+        <v>414</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C8" s="8" t="s">
         <v>1889</v>
       </c>
       <c r="D8">
@@ -40607,16 +40861,27 @@
         <v>45</v>
       </c>
       <c r="K8">
-        <f t="shared" ref="K8:K12" si="0">SUM(D8:J8)</f>
+        <f>SUM(D8:J8)</f>
         <v>774</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" ref="L8:L12" si="1">IF(K8&gt;900,"high","low")</f>
+        <f t="shared" ref="L8:L12" si="0">IF(K8&gt;=900,"High","Low")</f>
+        <v>Low</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" ref="M8:M12" si="1">IF(K8&gt;=900,"High",IF(K8&lt;=800,"Low","Mid"))</f>
+        <v>Low</v>
+      </c>
+      <c r="N8" t="str" cm="1">
+        <f t="array" ref="N8">_xlfn.IFS(K8&gt;=900,"high",K8&lt;900,"low")</f>
         <v>low</v>
       </c>
-    </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C9" s="9" t="s">
+      <c r="Q8" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C9" s="8" t="s">
         <v>1890</v>
       </c>
       <c r="D9">
@@ -40641,16 +40906,27 @@
         <v>153</v>
       </c>
       <c r="K9">
+        <f t="shared" ref="K9:K12" si="2">SUM(D9:J9)</f>
+        <v>794</v>
+      </c>
+      <c r="L9" t="str">
         <f t="shared" si="0"/>
-        <v>794</v>
-      </c>
-      <c r="L9" t="str">
+        <v>Low</v>
+      </c>
+      <c r="M9" t="str">
         <f t="shared" si="1"/>
+        <v>Low</v>
+      </c>
+      <c r="N9" t="str" cm="1">
+        <f t="array" ref="N9">_xlfn.IFS(K9&gt;=900,"high",K9&lt;900,"low")</f>
         <v>low</v>
       </c>
-    </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C10" s="9" t="s">
+      <c r="Q9" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C10" s="8" t="s">
         <v>1891</v>
       </c>
       <c r="D10">
@@ -40675,16 +40951,24 @@
         <v>144</v>
       </c>
       <c r="K10">
+        <f t="shared" si="2"/>
+        <v>997</v>
+      </c>
+      <c r="L10" t="str">
         <f t="shared" si="0"/>
-        <v>997</v>
-      </c>
-      <c r="L10" t="str">
+        <v>High</v>
+      </c>
+      <c r="M10" t="str">
         <f t="shared" si="1"/>
+        <v>High</v>
+      </c>
+      <c r="N10" t="str" cm="1">
+        <f t="array" ref="N10">_xlfn.IFS(K10&gt;=900,"high",K10&lt;900,"low")</f>
         <v>high</v>
       </c>
     </row>
-    <row r="11" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C11" s="9" t="s">
+    <row r="11" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C11" s="8" t="s">
         <v>1892</v>
       </c>
       <c r="D11">
@@ -40709,16 +40993,24 @@
         <v>63</v>
       </c>
       <c r="K11">
+        <f t="shared" si="2"/>
+        <v>828</v>
+      </c>
+      <c r="L11" t="str">
         <f t="shared" si="0"/>
-        <v>828</v>
-      </c>
-      <c r="L11" t="str">
+        <v>Low</v>
+      </c>
+      <c r="M11" t="str">
         <f t="shared" si="1"/>
+        <v>Mid</v>
+      </c>
+      <c r="N11" t="str" cm="1">
+        <f t="array" ref="N11">_xlfn.IFS(K11&gt;=900,"high",K11&lt;900,"low")</f>
         <v>low</v>
       </c>
     </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.35">
-      <c r="C12" s="9" t="s">
+    <row r="12" spans="3:17" x14ac:dyDescent="0.35">
+      <c r="C12" s="8" t="s">
         <v>1893</v>
       </c>
       <c r="D12">
@@ -40743,11 +41035,19 @@
         <v>108</v>
       </c>
       <c r="K12">
+        <f t="shared" si="2"/>
+        <v>925</v>
+      </c>
+      <c r="L12" t="str">
         <f t="shared" si="0"/>
-        <v>925</v>
-      </c>
-      <c r="L12" t="str">
+        <v>High</v>
+      </c>
+      <c r="M12" t="str">
         <f t="shared" si="1"/>
+        <v>High</v>
+      </c>
+      <c r="N12" t="str" cm="1">
+        <f t="array" ref="N12">_xlfn.IFS(K12&gt;=900,"high",K12&lt;900,"low")</f>
         <v>high</v>
       </c>
     </row>
